--- a/ELJUVY_0417/eljuvy.xlsx
+++ b/ELJUVY_0417/eljuvy.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Suli\4.félév\Operációs rendszerek\ELJUVY_0417\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C17D1C33-CAB9-48A1-9FD4-000AB1146699}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1092DF0C-D17B-4221-890B-1DD93C2950FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{210BA489-3838-42B3-8157-9C44F326F1F2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{210BA489-3838-42B3-8157-9C44F326F1F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
     <sheet name="Munka2" sheetId="2" r:id="rId2"/>
+    <sheet name="Munka3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="44">
   <si>
     <t>ÖSSES ERŐFORRÁS</t>
   </si>
@@ -111,12 +112,72 @@
   <si>
     <t>Tehát a rendszer biztonságosan fut</t>
   </si>
+  <si>
+    <t>First Fit</t>
+  </si>
+  <si>
+    <t>Szabad területek: 30K 35K 15K 25K 75K 45K</t>
+  </si>
+  <si>
+    <t>Foglalási igény: 39K 40K 33K 20K 21K</t>
+  </si>
+  <si>
+    <t>Szabad területek</t>
+  </si>
+  <si>
+    <t>FOGLALÁS</t>
+  </si>
+  <si>
+    <t>Töredezettség</t>
+  </si>
+  <si>
+    <t>Szabad particiók:</t>
+  </si>
+  <si>
+    <t>40/35</t>
+  </si>
+  <si>
+    <t>40/5</t>
+  </si>
+  <si>
+    <t>20/10</t>
+  </si>
+  <si>
+    <t>24/11</t>
+  </si>
+  <si>
+    <t>Nem sikerült foglalni:</t>
+  </si>
+  <si>
+    <t>Maradékok:</t>
+  </si>
+  <si>
+    <t>Túl kicsi blokk:</t>
+  </si>
+  <si>
+    <t>Össz:</t>
+  </si>
+  <si>
+    <t>Legkisebb:</t>
+  </si>
+  <si>
+    <t>elveszett: (maradék + túl kicsi + töredezettség) / szabad területek össz</t>
+  </si>
+  <si>
+    <t>Elveszett memóriaterület</t>
+  </si>
+  <si>
+    <t>Blokk méret:</t>
+  </si>
+  <si>
+    <t>A nem foglalt blokk kimarad</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -178,8 +239,32 @@
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -192,8 +277,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="15">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -355,11 +458,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -485,15 +604,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -578,9 +688,145 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="1" fillId="3" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="1" fillId="3" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
+    <cellStyle name="Százalék" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -908,33 +1154,33 @@
     <col min="19" max="16384" width="8.88671875" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:18" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C2" s="43" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="44"/>
-      <c r="E2" s="45"/>
-    </row>
-    <row r="3" spans="2:18" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C3" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="47" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="48" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="2:18" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C4" s="54">
+    <row r="1" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C2" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="74"/>
+      <c r="E2" s="75"/>
+    </row>
+    <row r="3" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="44" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="45" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C4" s="51">
         <v>10</v>
       </c>
-      <c r="D4" s="55">
-        <v>5</v>
-      </c>
-      <c r="E4" s="56">
+      <c r="D4" s="52">
+        <v>5</v>
+      </c>
+      <c r="E4" s="53">
         <v>7</v>
       </c>
       <c r="L4" s="18" t="s">
@@ -944,37 +1190,37 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="2:18" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:18" x14ac:dyDescent="0.3">
       <c r="C5" s="16"/>
       <c r="D5" s="16"/>
       <c r="E5" s="16"/>
     </row>
-    <row r="6" spans="2:18" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="7" spans="2:18" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C7" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="44"/>
-      <c r="E7" s="45"/>
-      <c r="G7" s="43" t="s">
+    <row r="6" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="7" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C7" s="73" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="74"/>
+      <c r="E7" s="75"/>
+      <c r="G7" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="44"/>
-      <c r="I7" s="45"/>
+      <c r="H7" s="74"/>
+      <c r="I7" s="75"/>
       <c r="J7" s="16"/>
-      <c r="K7" s="43" t="s">
+      <c r="K7" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="L7" s="44"/>
-      <c r="M7" s="45"/>
+      <c r="L7" s="74"/>
+      <c r="M7" s="75"/>
       <c r="N7" s="16"/>
-      <c r="P7" s="43" t="s">
+      <c r="P7" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="Q7" s="44"/>
-      <c r="R7" s="45"/>
-    </row>
-    <row r="8" spans="2:18" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q7" s="74"/>
+      <c r="R7" s="75"/>
+    </row>
+    <row r="8" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C8" s="15" t="s">
         <v>1</v>
       </c>
@@ -1004,60 +1250,60 @@
         <v>3</v>
       </c>
       <c r="N8" s="16"/>
-      <c r="P8" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="47" t="s">
-        <v>2</v>
-      </c>
-      <c r="R8" s="48" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="2:18" s="18" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="49" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="50">
-        <v>7</v>
-      </c>
-      <c r="D9" s="51">
-        <v>5</v>
-      </c>
-      <c r="E9" s="52">
-        <v>3</v>
-      </c>
-      <c r="G9" s="50">
-        <v>0</v>
-      </c>
-      <c r="H9" s="51">
-        <v>1</v>
-      </c>
-      <c r="I9" s="52">
+      <c r="P8" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="44" t="s">
+        <v>2</v>
+      </c>
+      <c r="R8" s="45" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B9" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="47">
+        <v>7</v>
+      </c>
+      <c r="D9" s="48">
+        <v>5</v>
+      </c>
+      <c r="E9" s="49">
+        <v>3</v>
+      </c>
+      <c r="G9" s="47">
+        <v>0</v>
+      </c>
+      <c r="H9" s="48">
+        <v>1</v>
+      </c>
+      <c r="I9" s="49">
         <v>0</v>
       </c>
       <c r="J9" s="16"/>
-      <c r="K9" s="50">
-        <v>7</v>
-      </c>
-      <c r="L9" s="51">
-        <v>4</v>
-      </c>
-      <c r="M9" s="52">
+      <c r="K9" s="47">
+        <v>7</v>
+      </c>
+      <c r="L9" s="48">
+        <v>4</v>
+      </c>
+      <c r="M9" s="49">
         <v>3</v>
       </c>
       <c r="N9" s="16"/>
-      <c r="P9" s="50">
+      <c r="P9" s="47">
         <v>10</v>
       </c>
-      <c r="Q9" s="51">
-        <v>5</v>
-      </c>
-      <c r="R9" s="52">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="2:18" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q9" s="48">
+        <v>5</v>
+      </c>
+      <c r="R9" s="49">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1093,17 +1339,17 @@
       <c r="N10" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="P10" s="54">
+      <c r="P10" s="51">
         <v>8</v>
       </c>
-      <c r="Q10" s="55">
-        <v>2</v>
-      </c>
-      <c r="R10" s="56">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="2:18" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q10" s="52">
+        <v>2</v>
+      </c>
+      <c r="R10" s="53">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="14" t="s">
         <v>7</v>
       </c>
@@ -1136,17 +1382,17 @@
         <v>0</v>
       </c>
       <c r="N11" s="16"/>
-      <c r="P11" s="46">
-        <v>2</v>
-      </c>
-      <c r="Q11" s="47">
-        <v>3</v>
-      </c>
-      <c r="R11" s="48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="2:18" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P11" s="43">
+        <v>2</v>
+      </c>
+      <c r="Q11" s="44">
+        <v>3</v>
+      </c>
+      <c r="R11" s="45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B12" s="14" t="s">
         <v>8</v>
       </c>
@@ -1180,82 +1426,82 @@
       </c>
       <c r="N12" s="16"/>
     </row>
-    <row r="13" spans="2:18" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="53" t="s">
+    <row r="13" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="54">
-        <v>4</v>
-      </c>
-      <c r="D13" s="55">
-        <v>3</v>
-      </c>
-      <c r="E13" s="56">
-        <v>3</v>
-      </c>
-      <c r="G13" s="54">
-        <v>0</v>
-      </c>
-      <c r="H13" s="55">
-        <v>0</v>
-      </c>
-      <c r="I13" s="56">
+      <c r="C13" s="51">
+        <v>4</v>
+      </c>
+      <c r="D13" s="52">
+        <v>3</v>
+      </c>
+      <c r="E13" s="53">
+        <v>3</v>
+      </c>
+      <c r="G13" s="51">
+        <v>0</v>
+      </c>
+      <c r="H13" s="52">
+        <v>0</v>
+      </c>
+      <c r="I13" s="53">
         <v>2</v>
       </c>
       <c r="J13" s="16"/>
-      <c r="K13" s="54">
-        <v>4</v>
-      </c>
-      <c r="L13" s="55">
-        <v>3</v>
-      </c>
-      <c r="M13" s="56">
+      <c r="K13" s="51">
+        <v>4</v>
+      </c>
+      <c r="L13" s="52">
+        <v>3</v>
+      </c>
+      <c r="M13" s="53">
         <v>1</v>
       </c>
       <c r="N13" s="16"/>
-      <c r="P13" s="57" t="s">
+      <c r="P13" s="54" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="2:18" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G14" s="46">
+    <row r="14" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G14" s="43">
         <v>8</v>
       </c>
-      <c r="H14" s="47">
-        <v>2</v>
-      </c>
-      <c r="I14" s="48">
+      <c r="H14" s="44">
+        <v>2</v>
+      </c>
+      <c r="I14" s="45">
         <v>7</v>
       </c>
       <c r="J14" s="16"/>
     </row>
-    <row r="16" spans="2:18" s="69" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="17" spans="2:18" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="2:18" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C18" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="D18" s="44"/>
-      <c r="E18" s="45"/>
-      <c r="G18" s="43" t="s">
+    <row r="16" spans="2:18" s="66" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="17" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="18" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C18" s="73" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="74"/>
+      <c r="E18" s="75"/>
+      <c r="G18" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="H18" s="44"/>
-      <c r="I18" s="45"/>
+      <c r="H18" s="74"/>
+      <c r="I18" s="75"/>
       <c r="J18" s="16"/>
-      <c r="K18" s="43" t="s">
+      <c r="K18" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="L18" s="44"/>
-      <c r="M18" s="45"/>
+      <c r="L18" s="74"/>
+      <c r="M18" s="75"/>
       <c r="N18" s="16"/>
-      <c r="P18" s="43" t="s">
+      <c r="P18" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="Q18" s="44"/>
-      <c r="R18" s="45"/>
-    </row>
-    <row r="19" spans="2:18" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q18" s="74"/>
+      <c r="R18" s="75"/>
+    </row>
+    <row r="19" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C19" s="15" t="s">
         <v>1</v>
       </c>
@@ -1285,60 +1531,60 @@
         <v>3</v>
       </c>
       <c r="N19" s="16"/>
-      <c r="P19" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q19" s="47" t="s">
-        <v>2</v>
-      </c>
-      <c r="R19" s="48" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="2:18" s="18" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="49" t="s">
-        <v>5</v>
-      </c>
-      <c r="C20" s="50">
-        <v>7</v>
-      </c>
-      <c r="D20" s="51">
-        <v>5</v>
-      </c>
-      <c r="E20" s="52">
-        <v>3</v>
-      </c>
-      <c r="G20" s="50">
-        <v>0</v>
-      </c>
-      <c r="H20" s="51">
-        <v>1</v>
-      </c>
-      <c r="I20" s="52">
+      <c r="P19" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="44" t="s">
+        <v>2</v>
+      </c>
+      <c r="R19" s="45" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B20" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="47">
+        <v>7</v>
+      </c>
+      <c r="D20" s="48">
+        <v>5</v>
+      </c>
+      <c r="E20" s="49">
+        <v>3</v>
+      </c>
+      <c r="G20" s="47">
+        <v>0</v>
+      </c>
+      <c r="H20" s="48">
+        <v>1</v>
+      </c>
+      <c r="I20" s="49">
         <v>0</v>
       </c>
       <c r="J20" s="16"/>
-      <c r="K20" s="50">
-        <v>7</v>
-      </c>
-      <c r="L20" s="51">
-        <v>4</v>
-      </c>
-      <c r="M20" s="52">
+      <c r="K20" s="47">
+        <v>7</v>
+      </c>
+      <c r="L20" s="48">
+        <v>4</v>
+      </c>
+      <c r="M20" s="49">
         <v>3</v>
       </c>
       <c r="N20" s="16"/>
-      <c r="P20" s="50">
+      <c r="P20" s="47">
         <v>10</v>
       </c>
-      <c r="Q20" s="51">
-        <v>5</v>
-      </c>
-      <c r="R20" s="52">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="2:18" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q20" s="48">
+        <v>5</v>
+      </c>
+      <c r="R20" s="49">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="14" t="s">
         <v>6</v>
       </c>
@@ -1371,17 +1617,17 @@
         <v>0</v>
       </c>
       <c r="N21" s="16"/>
-      <c r="P21" s="54">
-        <v>5</v>
-      </c>
-      <c r="Q21" s="55">
-        <v>2</v>
-      </c>
-      <c r="R21" s="56">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="2:18" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P21" s="51">
+        <v>5</v>
+      </c>
+      <c r="Q21" s="52">
+        <v>2</v>
+      </c>
+      <c r="R21" s="53">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="14" t="s">
         <v>7</v>
       </c>
@@ -1414,17 +1660,17 @@
         <v>0</v>
       </c>
       <c r="N22" s="16"/>
-      <c r="P22" s="46">
-        <v>5</v>
-      </c>
-      <c r="Q22" s="47">
-        <v>3</v>
-      </c>
-      <c r="R22" s="48">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="2:18" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P22" s="43">
+        <v>5</v>
+      </c>
+      <c r="Q22" s="44">
+        <v>3</v>
+      </c>
+      <c r="R22" s="45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
         <v>8</v>
       </c>
@@ -1461,82 +1707,82 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="2:18" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="70" t="s">
+    <row r="24" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="C24" s="71">
-        <v>4</v>
-      </c>
-      <c r="D24" s="72">
-        <v>3</v>
-      </c>
-      <c r="E24" s="73">
-        <v>3</v>
-      </c>
-      <c r="F24" s="74"/>
-      <c r="G24" s="71">
-        <v>0</v>
-      </c>
-      <c r="H24" s="72">
-        <v>0</v>
-      </c>
-      <c r="I24" s="73">
-        <v>2</v>
-      </c>
-      <c r="J24" s="75"/>
-      <c r="K24" s="71">
-        <v>4</v>
-      </c>
-      <c r="L24" s="72">
-        <v>3</v>
-      </c>
-      <c r="M24" s="73">
-        <v>1</v>
-      </c>
-      <c r="P24" s="57" t="s">
+      <c r="C24" s="68">
+        <v>4</v>
+      </c>
+      <c r="D24" s="69">
+        <v>3</v>
+      </c>
+      <c r="E24" s="70">
+        <v>3</v>
+      </c>
+      <c r="F24" s="71"/>
+      <c r="G24" s="68">
+        <v>0</v>
+      </c>
+      <c r="H24" s="69">
+        <v>0</v>
+      </c>
+      <c r="I24" s="70">
+        <v>2</v>
+      </c>
+      <c r="J24" s="72"/>
+      <c r="K24" s="68">
+        <v>4</v>
+      </c>
+      <c r="L24" s="69">
+        <v>3</v>
+      </c>
+      <c r="M24" s="70">
+        <v>1</v>
+      </c>
+      <c r="P24" s="54" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="2:18" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G25" s="46">
-        <v>5</v>
-      </c>
-      <c r="H25" s="47">
-        <v>2</v>
-      </c>
-      <c r="I25" s="48">
+    <row r="25" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G25" s="43">
+        <v>5</v>
+      </c>
+      <c r="H25" s="44">
+        <v>2</v>
+      </c>
+      <c r="I25" s="45">
         <v>5</v>
       </c>
       <c r="J25" s="16"/>
     </row>
-    <row r="27" spans="2:18" s="69" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="28" spans="2:18" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="29" spans="2:18" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C29" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="D29" s="44"/>
-      <c r="E29" s="45"/>
-      <c r="G29" s="43" t="s">
+    <row r="27" spans="2:18" s="66" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="29" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C29" s="73" t="s">
+        <v>4</v>
+      </c>
+      <c r="D29" s="74"/>
+      <c r="E29" s="75"/>
+      <c r="G29" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="H29" s="44"/>
-      <c r="I29" s="45"/>
+      <c r="H29" s="74"/>
+      <c r="I29" s="75"/>
       <c r="J29" s="16"/>
-      <c r="K29" s="43" t="s">
+      <c r="K29" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="L29" s="44"/>
-      <c r="M29" s="45"/>
+      <c r="L29" s="74"/>
+      <c r="M29" s="75"/>
       <c r="N29" s="16"/>
-      <c r="P29" s="43" t="s">
+      <c r="P29" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="Q29" s="44"/>
-      <c r="R29" s="45"/>
-    </row>
-    <row r="30" spans="2:18" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q29" s="74"/>
+      <c r="R29" s="75"/>
+    </row>
+    <row r="30" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C30" s="15" t="s">
         <v>1</v>
       </c>
@@ -1566,17 +1812,17 @@
         <v>3</v>
       </c>
       <c r="N30" s="16"/>
-      <c r="P30" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q30" s="47" t="s">
-        <v>2</v>
-      </c>
-      <c r="R30" s="48" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="2:18" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P30" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q30" s="44" t="s">
+        <v>2</v>
+      </c>
+      <c r="R30" s="45" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B31" s="10" t="s">
         <v>5</v>
       </c>
@@ -1612,17 +1858,17 @@
       <c r="N31" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="P31" s="50">
+      <c r="P31" s="47">
         <v>10</v>
       </c>
-      <c r="Q31" s="51">
-        <v>5</v>
-      </c>
-      <c r="R31" s="52">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="32" spans="2:18" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q31" s="48">
+        <v>5</v>
+      </c>
+      <c r="R31" s="49">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B32" s="34" t="s">
         <v>6</v>
       </c>
@@ -1655,17 +1901,17 @@
         <v>0</v>
       </c>
       <c r="N32" s="16"/>
-      <c r="P32" s="54">
-        <v>3</v>
-      </c>
-      <c r="Q32" s="55">
-        <v>1</v>
-      </c>
-      <c r="R32" s="56">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P32" s="51">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="52">
+        <v>1</v>
+      </c>
+      <c r="R32" s="53">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B33" s="14" t="s">
         <v>7</v>
       </c>
@@ -1698,17 +1944,17 @@
         <v>0</v>
       </c>
       <c r="N33" s="16"/>
-      <c r="P33" s="46">
-        <v>7</v>
-      </c>
-      <c r="Q33" s="47">
-        <v>4</v>
-      </c>
-      <c r="R33" s="48">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P33" s="43">
+        <v>7</v>
+      </c>
+      <c r="Q33" s="44">
+        <v>4</v>
+      </c>
+      <c r="R33" s="45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" s="5"/>
       <c r="B34" s="34" t="s">
         <v>8</v>
@@ -1744,83 +1990,83 @@
       </c>
       <c r="N34" s="3"/>
     </row>
-    <row r="35" spans="1:18" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="70" t="s">
+    <row r="35" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B35" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="C35" s="71">
-        <v>4</v>
-      </c>
-      <c r="D35" s="72">
-        <v>3</v>
-      </c>
-      <c r="E35" s="73">
-        <v>3</v>
-      </c>
-      <c r="F35" s="74"/>
-      <c r="G35" s="71">
-        <v>0</v>
-      </c>
-      <c r="H35" s="72">
-        <v>0</v>
-      </c>
-      <c r="I35" s="73">
-        <v>2</v>
-      </c>
-      <c r="J35" s="75"/>
-      <c r="K35" s="71">
-        <v>4</v>
-      </c>
-      <c r="L35" s="72">
-        <v>3</v>
-      </c>
-      <c r="M35" s="73">
+      <c r="C35" s="68">
+        <v>4</v>
+      </c>
+      <c r="D35" s="69">
+        <v>3</v>
+      </c>
+      <c r="E35" s="70">
+        <v>3</v>
+      </c>
+      <c r="F35" s="71"/>
+      <c r="G35" s="68">
+        <v>0</v>
+      </c>
+      <c r="H35" s="69">
+        <v>0</v>
+      </c>
+      <c r="I35" s="70">
+        <v>2</v>
+      </c>
+      <c r="J35" s="72"/>
+      <c r="K35" s="68">
+        <v>4</v>
+      </c>
+      <c r="L35" s="69">
+        <v>3</v>
+      </c>
+      <c r="M35" s="70">
         <v>1</v>
       </c>
       <c r="N35" s="16"/>
-      <c r="P35" s="57" t="s">
+      <c r="P35" s="54" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G36" s="46">
-        <v>3</v>
-      </c>
-      <c r="H36" s="47">
-        <v>1</v>
-      </c>
-      <c r="I36" s="48">
+    <row r="36" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G36" s="43">
+        <v>3</v>
+      </c>
+      <c r="H36" s="44">
+        <v>1</v>
+      </c>
+      <c r="I36" s="45">
         <v>4</v>
       </c>
       <c r="J36" s="16"/>
     </row>
-    <row r="38" spans="1:18" s="69" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="39" spans="1:18" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="40" spans="1:18" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C40" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="D40" s="44"/>
-      <c r="E40" s="45"/>
-      <c r="G40" s="43" t="s">
+    <row r="38" spans="1:18" s="66" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="39" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="40" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C40" s="73" t="s">
+        <v>4</v>
+      </c>
+      <c r="D40" s="74"/>
+      <c r="E40" s="75"/>
+      <c r="G40" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="H40" s="44"/>
-      <c r="I40" s="45"/>
+      <c r="H40" s="74"/>
+      <c r="I40" s="75"/>
       <c r="J40" s="16"/>
-      <c r="K40" s="43" t="s">
+      <c r="K40" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="L40" s="44"/>
-      <c r="M40" s="45"/>
+      <c r="L40" s="74"/>
+      <c r="M40" s="75"/>
       <c r="N40" s="16"/>
-      <c r="P40" s="43" t="s">
+      <c r="P40" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="Q40" s="44"/>
-      <c r="R40" s="45"/>
-    </row>
-    <row r="41" spans="1:18" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q40" s="74"/>
+      <c r="R40" s="75"/>
+    </row>
+    <row r="41" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C41" s="15" t="s">
         <v>1</v>
       </c>
@@ -1850,61 +2096,61 @@
         <v>3</v>
       </c>
       <c r="N41" s="16"/>
-      <c r="P41" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q41" s="47" t="s">
-        <v>2</v>
-      </c>
-      <c r="R41" s="48" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" s="18" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="61" t="s">
-        <v>5</v>
-      </c>
-      <c r="C42" s="62">
-        <v>7</v>
-      </c>
-      <c r="D42" s="63">
-        <v>5</v>
-      </c>
-      <c r="E42" s="64">
+      <c r="P41" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q41" s="44" t="s">
+        <v>2</v>
+      </c>
+      <c r="R41" s="45" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B42" s="58" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42" s="59">
+        <v>7</v>
+      </c>
+      <c r="D42" s="60">
+        <v>5</v>
+      </c>
+      <c r="E42" s="61">
         <v>3</v>
       </c>
       <c r="F42" s="38"/>
-      <c r="G42" s="62">
-        <v>0</v>
-      </c>
-      <c r="H42" s="63">
-        <v>1</v>
-      </c>
-      <c r="I42" s="64">
+      <c r="G42" s="59">
+        <v>0</v>
+      </c>
+      <c r="H42" s="60">
+        <v>1</v>
+      </c>
+      <c r="I42" s="61">
         <v>0</v>
       </c>
       <c r="J42" s="36"/>
-      <c r="K42" s="62">
-        <v>7</v>
-      </c>
-      <c r="L42" s="63">
-        <v>4</v>
-      </c>
-      <c r="M42" s="64">
+      <c r="K42" s="59">
+        <v>7</v>
+      </c>
+      <c r="L42" s="60">
+        <v>4</v>
+      </c>
+      <c r="M42" s="61">
         <v>3</v>
       </c>
       <c r="N42" s="16"/>
-      <c r="P42" s="50">
+      <c r="P42" s="47">
         <v>10</v>
       </c>
-      <c r="Q42" s="51">
-        <v>5</v>
-      </c>
-      <c r="R42" s="52">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q42" s="48">
+        <v>5</v>
+      </c>
+      <c r="R42" s="49">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B43" s="34" t="s">
         <v>6</v>
       </c>
@@ -1937,17 +2183,17 @@
         <v>0</v>
       </c>
       <c r="N43" s="16"/>
-      <c r="P43" s="54">
-        <v>3</v>
-      </c>
-      <c r="Q43" s="55">
-        <v>0</v>
-      </c>
-      <c r="R43" s="56">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P43" s="51">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="52">
+        <v>0</v>
+      </c>
+      <c r="R43" s="53">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
@@ -1983,17 +2229,17 @@
       <c r="N44" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="P44" s="46">
-        <v>7</v>
-      </c>
-      <c r="Q44" s="47">
-        <v>5</v>
-      </c>
-      <c r="R44" s="48">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P44" s="43">
+        <v>7</v>
+      </c>
+      <c r="Q44" s="44">
+        <v>5</v>
+      </c>
+      <c r="R44" s="45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B45" s="34" t="s">
         <v>8</v>
       </c>
@@ -2028,83 +2274,83 @@
       </c>
       <c r="N45" s="16"/>
     </row>
-    <row r="46" spans="1:18" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B46" s="70" t="s">
+    <row r="46" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B46" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="C46" s="71">
-        <v>4</v>
-      </c>
-      <c r="D46" s="72">
-        <v>3</v>
-      </c>
-      <c r="E46" s="73">
-        <v>3</v>
-      </c>
-      <c r="F46" s="74"/>
-      <c r="G46" s="71">
-        <v>0</v>
-      </c>
-      <c r="H46" s="72">
-        <v>0</v>
-      </c>
-      <c r="I46" s="73">
-        <v>2</v>
-      </c>
-      <c r="J46" s="75"/>
-      <c r="K46" s="71">
-        <v>4</v>
-      </c>
-      <c r="L46" s="72">
-        <v>3</v>
-      </c>
-      <c r="M46" s="73">
+      <c r="C46" s="68">
+        <v>4</v>
+      </c>
+      <c r="D46" s="69">
+        <v>3</v>
+      </c>
+      <c r="E46" s="70">
+        <v>3</v>
+      </c>
+      <c r="F46" s="71"/>
+      <c r="G46" s="68">
+        <v>0</v>
+      </c>
+      <c r="H46" s="69">
+        <v>0</v>
+      </c>
+      <c r="I46" s="70">
+        <v>2</v>
+      </c>
+      <c r="J46" s="72"/>
+      <c r="K46" s="68">
+        <v>4</v>
+      </c>
+      <c r="L46" s="69">
+        <v>3</v>
+      </c>
+      <c r="M46" s="70">
         <v>1</v>
       </c>
       <c r="N46" s="16"/>
-      <c r="P46" s="57" t="s">
+      <c r="P46" s="54" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G47" s="46">
-        <v>3</v>
-      </c>
-      <c r="H47" s="47">
-        <v>0</v>
-      </c>
-      <c r="I47" s="48">
+    <row r="47" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G47" s="43">
+        <v>3</v>
+      </c>
+      <c r="H47" s="44">
+        <v>0</v>
+      </c>
+      <c r="I47" s="45">
         <v>4</v>
       </c>
       <c r="J47" s="16"/>
     </row>
-    <row r="49" spans="2:18" s="69" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="50" spans="2:18" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="51" spans="2:18" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C51" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="D51" s="44"/>
-      <c r="E51" s="45"/>
-      <c r="G51" s="43" t="s">
+    <row r="49" spans="2:18" s="66" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="50" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="51" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C51" s="73" t="s">
+        <v>4</v>
+      </c>
+      <c r="D51" s="74"/>
+      <c r="E51" s="75"/>
+      <c r="G51" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="H51" s="44"/>
-      <c r="I51" s="45"/>
+      <c r="H51" s="74"/>
+      <c r="I51" s="75"/>
       <c r="J51" s="16"/>
-      <c r="K51" s="43" t="s">
+      <c r="K51" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="L51" s="44"/>
-      <c r="M51" s="45"/>
+      <c r="L51" s="74"/>
+      <c r="M51" s="75"/>
       <c r="N51" s="16"/>
-      <c r="P51" s="43" t="s">
+      <c r="P51" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="Q51" s="44"/>
-      <c r="R51" s="45"/>
-    </row>
-    <row r="52" spans="2:18" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q51" s="74"/>
+      <c r="R51" s="75"/>
+    </row>
+    <row r="52" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C52" s="15" t="s">
         <v>1</v>
       </c>
@@ -2134,61 +2380,61 @@
         <v>3</v>
       </c>
       <c r="N52" s="16"/>
-      <c r="P52" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q52" s="47" t="s">
-        <v>2</v>
-      </c>
-      <c r="R52" s="48" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="2:18" s="18" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="61" t="s">
-        <v>5</v>
-      </c>
-      <c r="C53" s="62">
-        <v>7</v>
-      </c>
-      <c r="D53" s="63">
-        <v>5</v>
-      </c>
-      <c r="E53" s="64">
+      <c r="P52" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q52" s="44" t="s">
+        <v>2</v>
+      </c>
+      <c r="R52" s="45" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B53" s="58" t="s">
+        <v>5</v>
+      </c>
+      <c r="C53" s="59">
+        <v>7</v>
+      </c>
+      <c r="D53" s="60">
+        <v>5</v>
+      </c>
+      <c r="E53" s="61">
         <v>3</v>
       </c>
       <c r="F53" s="38"/>
-      <c r="G53" s="62">
-        <v>0</v>
-      </c>
-      <c r="H53" s="63">
-        <v>1</v>
-      </c>
-      <c r="I53" s="64">
+      <c r="G53" s="59">
+        <v>0</v>
+      </c>
+      <c r="H53" s="60">
+        <v>1</v>
+      </c>
+      <c r="I53" s="61">
         <v>0</v>
       </c>
       <c r="J53" s="36"/>
-      <c r="K53" s="62">
-        <v>7</v>
-      </c>
-      <c r="L53" s="63">
-        <v>4</v>
-      </c>
-      <c r="M53" s="64">
+      <c r="K53" s="59">
+        <v>7</v>
+      </c>
+      <c r="L53" s="60">
+        <v>4</v>
+      </c>
+      <c r="M53" s="61">
         <v>3</v>
       </c>
       <c r="N53" s="16"/>
-      <c r="P53" s="50">
+      <c r="P53" s="47">
         <v>10</v>
       </c>
-      <c r="Q53" s="51">
-        <v>5</v>
-      </c>
-      <c r="R53" s="52">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="54" spans="2:18" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q53" s="48">
+        <v>5</v>
+      </c>
+      <c r="R53" s="49">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B54" s="34" t="s">
         <v>6</v>
       </c>
@@ -2221,17 +2467,17 @@
         <v>0</v>
       </c>
       <c r="N54" s="16"/>
-      <c r="P54" s="54">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="55">
-        <v>0</v>
-      </c>
-      <c r="R54" s="56">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="55" spans="2:18" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P54" s="51">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="52">
+        <v>0</v>
+      </c>
+      <c r="R54" s="53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B55" s="34" t="s">
         <v>7</v>
       </c>
@@ -2265,17 +2511,17 @@
         <v>0</v>
       </c>
       <c r="N55" s="3"/>
-      <c r="P55" s="46">
+      <c r="P55" s="43">
         <v>10</v>
       </c>
-      <c r="Q55" s="47">
-        <v>5</v>
-      </c>
-      <c r="R55" s="48">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="56" spans="2:18" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q55" s="44">
+        <v>5</v>
+      </c>
+      <c r="R55" s="45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B56" s="34" t="s">
         <v>8</v>
       </c>
@@ -2310,7 +2556,7 @@
       </c>
       <c r="N56" s="16"/>
     </row>
-    <row r="57" spans="2:18" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B57" s="6" t="s">
         <v>9</v>
       </c>
@@ -2346,24 +2592,37 @@
       <c r="N57" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="P57" s="57" t="s">
+      <c r="P57" s="54" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="58" spans="2:18" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G58" s="46">
-        <v>0</v>
-      </c>
-      <c r="H58" s="47">
-        <v>0</v>
-      </c>
-      <c r="I58" s="48">
+    <row r="58" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G58" s="43">
+        <v>0</v>
+      </c>
+      <c r="H58" s="44">
+        <v>0</v>
+      </c>
+      <c r="I58" s="45">
         <v>2</v>
       </c>
       <c r="J58" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="P7:R7"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="K18:M18"/>
+    <mergeCell ref="P18:R18"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="K29:M29"/>
+    <mergeCell ref="P29:R29"/>
     <mergeCell ref="C40:E40"/>
     <mergeCell ref="G40:I40"/>
     <mergeCell ref="K40:M40"/>
@@ -2372,19 +2631,6 @@
     <mergeCell ref="G51:I51"/>
     <mergeCell ref="K51:M51"/>
     <mergeCell ref="P51:R51"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="P18:R18"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="K29:M29"/>
-    <mergeCell ref="P29:R29"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="P7:R7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2402,7 +2648,7 @@
     <col min="7" max="9" width="7.33203125" style="42" customWidth="1"/>
     <col min="10" max="10" width="3.109375" style="42" customWidth="1"/>
     <col min="11" max="13" width="6.21875" style="42" customWidth="1"/>
-    <col min="14" max="14" width="8.88671875" style="60"/>
+    <col min="14" max="14" width="8.88671875" style="57"/>
     <col min="15" max="15" width="2.33203125" style="42" customWidth="1"/>
     <col min="16" max="18" width="7.88671875" style="42" customWidth="1"/>
     <col min="19" max="16384" width="8.88671875" style="42"/>
@@ -2432,11 +2678,11 @@
     <row r="2" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="18"/>
       <c r="B2" s="18"/>
-      <c r="C2" s="43" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="44"/>
-      <c r="E2" s="45"/>
+      <c r="C2" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="74"/>
+      <c r="E2" s="75"/>
       <c r="F2" s="18"/>
       <c r="G2" s="18"/>
       <c r="H2" s="18"/>
@@ -2455,13 +2701,13 @@
     <row r="3" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="18"/>
       <c r="B3" s="18"/>
-      <c r="C3" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="47" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="48" t="s">
+      <c r="C3" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="44" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="45" t="s">
         <v>3</v>
       </c>
       <c r="F3" s="18"/>
@@ -2555,30 +2801,30 @@
     <row r="7" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="18"/>
       <c r="B7" s="18"/>
-      <c r="C7" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="44"/>
-      <c r="E7" s="45"/>
+      <c r="C7" s="73" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="74"/>
+      <c r="E7" s="75"/>
       <c r="F7" s="18"/>
-      <c r="G7" s="43" t="s">
+      <c r="G7" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="44"/>
-      <c r="I7" s="45"/>
+      <c r="H7" s="74"/>
+      <c r="I7" s="75"/>
       <c r="J7" s="16"/>
-      <c r="K7" s="43" t="s">
+      <c r="K7" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="L7" s="44"/>
-      <c r="M7" s="45"/>
+      <c r="L7" s="74"/>
+      <c r="M7" s="75"/>
       <c r="N7" s="3"/>
       <c r="O7" s="18"/>
-      <c r="P7" s="43" t="s">
+      <c r="P7" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="Q7" s="44"/>
-      <c r="R7" s="45"/>
+      <c r="Q7" s="74"/>
+      <c r="R7" s="75"/>
       <c r="S7" s="18"/>
     </row>
     <row r="8" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2615,49 +2861,49 @@
       </c>
       <c r="N8" s="3"/>
       <c r="O8" s="18"/>
-      <c r="P8" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="47" t="s">
-        <v>2</v>
-      </c>
-      <c r="R8" s="48" t="s">
+      <c r="P8" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="44" t="s">
+        <v>2</v>
+      </c>
+      <c r="R8" s="45" t="s">
         <v>3</v>
       </c>
       <c r="S8" s="18"/>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" s="18"/>
-      <c r="B9" s="49" t="s">
+      <c r="B9" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="50">
-        <v>7</v>
-      </c>
-      <c r="D9" s="51">
-        <v>5</v>
-      </c>
-      <c r="E9" s="52">
+      <c r="C9" s="47">
+        <v>7</v>
+      </c>
+      <c r="D9" s="48">
+        <v>5</v>
+      </c>
+      <c r="E9" s="49">
         <v>3</v>
       </c>
       <c r="F9" s="18"/>
-      <c r="G9" s="50">
-        <v>0</v>
-      </c>
-      <c r="H9" s="51">
-        <v>1</v>
-      </c>
-      <c r="I9" s="52">
+      <c r="G9" s="47">
+        <v>0</v>
+      </c>
+      <c r="H9" s="48">
+        <v>1</v>
+      </c>
+      <c r="I9" s="49">
         <v>0</v>
       </c>
       <c r="J9" s="16"/>
-      <c r="K9" s="50">
-        <v>7</v>
-      </c>
-      <c r="L9" s="51">
-        <v>4</v>
-      </c>
-      <c r="M9" s="52">
+      <c r="K9" s="47">
+        <v>7</v>
+      </c>
+      <c r="L9" s="48">
+        <v>4</v>
+      </c>
+      <c r="M9" s="49">
         <v>3</v>
       </c>
       <c r="N9" s="3"/>
@@ -2812,41 +3058,41 @@
     </row>
     <row r="13" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="18"/>
-      <c r="B13" s="53" t="s">
+      <c r="B13" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="54">
-        <v>4</v>
-      </c>
-      <c r="D13" s="55">
-        <v>3</v>
-      </c>
-      <c r="E13" s="56">
+      <c r="C13" s="51">
+        <v>4</v>
+      </c>
+      <c r="D13" s="52">
+        <v>3</v>
+      </c>
+      <c r="E13" s="53">
         <v>3</v>
       </c>
       <c r="F13" s="18"/>
-      <c r="G13" s="54">
-        <v>0</v>
-      </c>
-      <c r="H13" s="55">
-        <v>0</v>
-      </c>
-      <c r="I13" s="56">
+      <c r="G13" s="51">
+        <v>0</v>
+      </c>
+      <c r="H13" s="52">
+        <v>0</v>
+      </c>
+      <c r="I13" s="53">
         <v>2</v>
       </c>
       <c r="J13" s="16"/>
-      <c r="K13" s="54">
-        <v>4</v>
-      </c>
-      <c r="L13" s="55">
-        <v>3</v>
-      </c>
-      <c r="M13" s="56">
+      <c r="K13" s="51">
+        <v>4</v>
+      </c>
+      <c r="L13" s="52">
+        <v>3</v>
+      </c>
+      <c r="M13" s="53">
         <v>1</v>
       </c>
       <c r="N13" s="3"/>
       <c r="O13" s="18"/>
-      <c r="P13" s="57" t="s">
+      <c r="P13" s="54" t="s">
         <v>19</v>
       </c>
       <c r="Q13" s="18"/>
@@ -2901,37 +3147,37 @@
       <c r="R15" s="18"/>
       <c r="S15" s="18"/>
     </row>
-    <row r="16" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="N16" s="59"/>
+    <row r="16" spans="1:19" s="55" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="N16" s="56"/>
     </row>
     <row r="17" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="18"/>
       <c r="B18" s="18"/>
-      <c r="C18" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="D18" s="44"/>
-      <c r="E18" s="45"/>
+      <c r="C18" s="73" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="74"/>
+      <c r="E18" s="75"/>
       <c r="F18" s="18"/>
-      <c r="G18" s="43" t="s">
+      <c r="G18" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="H18" s="44"/>
-      <c r="I18" s="45"/>
+      <c r="H18" s="74"/>
+      <c r="I18" s="75"/>
       <c r="J18" s="16"/>
-      <c r="K18" s="43" t="s">
+      <c r="K18" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="L18" s="44"/>
-      <c r="M18" s="45"/>
+      <c r="L18" s="74"/>
+      <c r="M18" s="75"/>
       <c r="N18" s="3"/>
       <c r="O18" s="18"/>
-      <c r="P18" s="43" t="s">
+      <c r="P18" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="Q18" s="44"/>
-      <c r="R18" s="45"/>
+      <c r="Q18" s="74"/>
+      <c r="R18" s="75"/>
     </row>
     <row r="19" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="18"/>
@@ -2967,48 +3213,48 @@
       </c>
       <c r="N19" s="3"/>
       <c r="O19" s="18"/>
-      <c r="P19" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q19" s="51" t="s">
-        <v>2</v>
-      </c>
-      <c r="R19" s="52" t="s">
+      <c r="P19" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="R19" s="49" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="18"/>
-      <c r="B20" s="49" t="s">
+      <c r="B20" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="50">
-        <v>7</v>
-      </c>
-      <c r="D20" s="51">
-        <v>5</v>
-      </c>
-      <c r="E20" s="52">
+      <c r="C20" s="47">
+        <v>7</v>
+      </c>
+      <c r="D20" s="48">
+        <v>5</v>
+      </c>
+      <c r="E20" s="49">
         <v>3</v>
       </c>
       <c r="F20" s="18"/>
-      <c r="G20" s="50">
-        <v>0</v>
-      </c>
-      <c r="H20" s="51">
-        <v>1</v>
-      </c>
-      <c r="I20" s="52">
+      <c r="G20" s="47">
+        <v>0</v>
+      </c>
+      <c r="H20" s="48">
+        <v>1</v>
+      </c>
+      <c r="I20" s="49">
         <v>0</v>
       </c>
       <c r="J20" s="16"/>
-      <c r="K20" s="50">
-        <v>7</v>
-      </c>
-      <c r="L20" s="51">
-        <v>4</v>
-      </c>
-      <c r="M20" s="52">
+      <c r="K20" s="47">
+        <v>7</v>
+      </c>
+      <c r="L20" s="48">
+        <v>4</v>
+      </c>
+      <c r="M20" s="49">
         <v>3</v>
       </c>
       <c r="N20" s="3"/>
@@ -3165,41 +3411,41 @@
     </row>
     <row r="24" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="18"/>
-      <c r="B24" s="53" t="s">
+      <c r="B24" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="C24" s="54">
-        <v>4</v>
-      </c>
-      <c r="D24" s="55">
-        <v>3</v>
-      </c>
-      <c r="E24" s="56">
+      <c r="C24" s="51">
+        <v>4</v>
+      </c>
+      <c r="D24" s="52">
+        <v>3</v>
+      </c>
+      <c r="E24" s="53">
         <v>3</v>
       </c>
       <c r="F24" s="18"/>
-      <c r="G24" s="54">
-        <v>0</v>
-      </c>
-      <c r="H24" s="55">
-        <v>0</v>
-      </c>
-      <c r="I24" s="56">
+      <c r="G24" s="51">
+        <v>0</v>
+      </c>
+      <c r="H24" s="52">
+        <v>0</v>
+      </c>
+      <c r="I24" s="53">
         <v>2</v>
       </c>
       <c r="J24" s="16"/>
-      <c r="K24" s="54">
-        <v>4</v>
-      </c>
-      <c r="L24" s="55">
-        <v>3</v>
-      </c>
-      <c r="M24" s="56">
+      <c r="K24" s="51">
+        <v>4</v>
+      </c>
+      <c r="L24" s="52">
+        <v>3</v>
+      </c>
+      <c r="M24" s="53">
         <v>1</v>
       </c>
       <c r="N24" s="3"/>
       <c r="O24" s="18"/>
-      <c r="P24" s="57" t="s">
+      <c r="P24" s="54" t="s">
         <v>20</v>
       </c>
       <c r="Q24" s="18"/>
@@ -3251,37 +3497,37 @@
       <c r="Q26" s="18"/>
       <c r="R26" s="18"/>
     </row>
-    <row r="27" spans="1:18" s="58" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="N27" s="59"/>
+    <row r="27" spans="1:18" s="55" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="N27" s="56"/>
     </row>
     <row r="28" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="29" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="18"/>
       <c r="B29" s="18"/>
-      <c r="C29" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="D29" s="44"/>
-      <c r="E29" s="45"/>
+      <c r="C29" s="73" t="s">
+        <v>4</v>
+      </c>
+      <c r="D29" s="74"/>
+      <c r="E29" s="75"/>
       <c r="F29" s="18"/>
-      <c r="G29" s="43" t="s">
+      <c r="G29" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="H29" s="44"/>
-      <c r="I29" s="45"/>
+      <c r="H29" s="74"/>
+      <c r="I29" s="75"/>
       <c r="J29" s="16"/>
-      <c r="K29" s="43" t="s">
+      <c r="K29" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="L29" s="44"/>
-      <c r="M29" s="45"/>
+      <c r="L29" s="74"/>
+      <c r="M29" s="75"/>
       <c r="N29" s="3"/>
       <c r="O29" s="18"/>
-      <c r="P29" s="43" t="s">
+      <c r="P29" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="Q29" s="44"/>
-      <c r="R29" s="45"/>
+      <c r="Q29" s="74"/>
+      <c r="R29" s="75"/>
     </row>
     <row r="30" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="18"/>
@@ -3317,13 +3563,13 @@
       </c>
       <c r="N30" s="3"/>
       <c r="O30" s="18"/>
-      <c r="P30" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q30" s="51" t="s">
-        <v>2</v>
-      </c>
-      <c r="R30" s="52" t="s">
+      <c r="P30" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q30" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="R30" s="49" t="s">
         <v>3</v>
       </c>
     </row>
@@ -3515,41 +3761,41 @@
     </row>
     <row r="35" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="18"/>
-      <c r="B35" s="53" t="s">
+      <c r="B35" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="C35" s="54">
-        <v>4</v>
-      </c>
-      <c r="D35" s="55">
-        <v>3</v>
-      </c>
-      <c r="E35" s="56">
+      <c r="C35" s="51">
+        <v>4</v>
+      </c>
+      <c r="D35" s="52">
+        <v>3</v>
+      </c>
+      <c r="E35" s="53">
         <v>3</v>
       </c>
       <c r="F35" s="18"/>
-      <c r="G35" s="54">
-        <v>0</v>
-      </c>
-      <c r="H35" s="55">
-        <v>0</v>
-      </c>
-      <c r="I35" s="56">
+      <c r="G35" s="51">
+        <v>0</v>
+      </c>
+      <c r="H35" s="52">
+        <v>0</v>
+      </c>
+      <c r="I35" s="53">
         <v>2</v>
       </c>
       <c r="J35" s="16"/>
-      <c r="K35" s="54">
-        <v>4</v>
-      </c>
-      <c r="L35" s="55">
-        <v>3</v>
-      </c>
-      <c r="M35" s="56">
+      <c r="K35" s="51">
+        <v>4</v>
+      </c>
+      <c r="L35" s="52">
+        <v>3</v>
+      </c>
+      <c r="M35" s="53">
         <v>1</v>
       </c>
       <c r="N35" s="3"/>
       <c r="O35" s="18"/>
-      <c r="P35" s="57" t="s">
+      <c r="P35" s="54" t="s">
         <v>22</v>
       </c>
       <c r="Q35" s="18"/>
@@ -3601,37 +3847,37 @@
       <c r="Q37" s="18"/>
       <c r="R37" s="18"/>
     </row>
-    <row r="38" spans="1:18" s="58" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="N38" s="59"/>
+    <row r="38" spans="1:18" s="55" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="N38" s="56"/>
     </row>
     <row r="39" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="40" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="18"/>
       <c r="B40" s="18"/>
-      <c r="C40" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="D40" s="44"/>
-      <c r="E40" s="45"/>
+      <c r="C40" s="73" t="s">
+        <v>4</v>
+      </c>
+      <c r="D40" s="74"/>
+      <c r="E40" s="75"/>
       <c r="F40" s="18"/>
-      <c r="G40" s="43" t="s">
+      <c r="G40" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="H40" s="44"/>
-      <c r="I40" s="45"/>
+      <c r="H40" s="74"/>
+      <c r="I40" s="75"/>
       <c r="J40" s="16"/>
-      <c r="K40" s="43" t="s">
+      <c r="K40" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="L40" s="44"/>
-      <c r="M40" s="45"/>
+      <c r="L40" s="74"/>
+      <c r="M40" s="75"/>
       <c r="N40" s="3"/>
       <c r="O40" s="18"/>
-      <c r="P40" s="43" t="s">
+      <c r="P40" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="Q40" s="44"/>
-      <c r="R40" s="45"/>
+      <c r="Q40" s="74"/>
+      <c r="R40" s="75"/>
     </row>
     <row r="41" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="18"/>
@@ -3667,48 +3913,48 @@
       </c>
       <c r="N41" s="3"/>
       <c r="O41" s="18"/>
-      <c r="P41" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q41" s="51" t="s">
-        <v>2</v>
-      </c>
-      <c r="R41" s="52" t="s">
+      <c r="P41" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q41" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="R41" s="49" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" s="18"/>
-      <c r="B42" s="61" t="s">
+      <c r="B42" s="58" t="s">
         <v>21</v>
       </c>
-      <c r="C42" s="62">
-        <v>7</v>
-      </c>
-      <c r="D42" s="63">
-        <v>5</v>
-      </c>
-      <c r="E42" s="64">
+      <c r="C42" s="59">
+        <v>7</v>
+      </c>
+      <c r="D42" s="60">
+        <v>5</v>
+      </c>
+      <c r="E42" s="61">
         <v>3</v>
       </c>
       <c r="F42" s="38"/>
-      <c r="G42" s="62">
-        <v>0</v>
-      </c>
-      <c r="H42" s="63">
-        <v>1</v>
-      </c>
-      <c r="I42" s="64">
+      <c r="G42" s="59">
+        <v>0</v>
+      </c>
+      <c r="H42" s="60">
+        <v>1</v>
+      </c>
+      <c r="I42" s="61">
         <v>0</v>
       </c>
       <c r="J42" s="36"/>
-      <c r="K42" s="62">
-        <v>7</v>
-      </c>
-      <c r="L42" s="63">
-        <v>4</v>
-      </c>
-      <c r="M42" s="64">
+      <c r="K42" s="59">
+        <v>7</v>
+      </c>
+      <c r="L42" s="60">
+        <v>4</v>
+      </c>
+      <c r="M42" s="61">
         <v>3</v>
       </c>
       <c r="N42" s="3"/>
@@ -3899,7 +4145,7 @@
         <v>15</v>
       </c>
       <c r="O46" s="18"/>
-      <c r="P46" s="57" t="s">
+      <c r="P46" s="54" t="s">
         <v>18</v>
       </c>
       <c r="Q46" s="18"/>
@@ -3951,37 +4197,37 @@
       <c r="Q48" s="18"/>
       <c r="R48" s="18"/>
     </row>
-    <row r="49" spans="1:18" s="58" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="N49" s="59"/>
+    <row r="49" spans="1:18" s="55" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="N49" s="56"/>
     </row>
     <row r="50" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="51" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="18"/>
       <c r="B51" s="18"/>
-      <c r="C51" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="D51" s="44"/>
-      <c r="E51" s="45"/>
+      <c r="C51" s="73" t="s">
+        <v>4</v>
+      </c>
+      <c r="D51" s="74"/>
+      <c r="E51" s="75"/>
       <c r="F51" s="18"/>
-      <c r="G51" s="43" t="s">
+      <c r="G51" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="H51" s="44"/>
-      <c r="I51" s="45"/>
+      <c r="H51" s="74"/>
+      <c r="I51" s="75"/>
       <c r="J51" s="16"/>
-      <c r="K51" s="43" t="s">
+      <c r="K51" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="L51" s="44"/>
-      <c r="M51" s="45"/>
+      <c r="L51" s="74"/>
+      <c r="M51" s="75"/>
       <c r="N51" s="3"/>
       <c r="O51" s="18"/>
-      <c r="P51" s="43" t="s">
+      <c r="P51" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="Q51" s="44"/>
-      <c r="R51" s="45"/>
+      <c r="Q51" s="74"/>
+      <c r="R51" s="75"/>
     </row>
     <row r="52" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="18"/>
@@ -4017,48 +4263,48 @@
       </c>
       <c r="N52" s="3"/>
       <c r="O52" s="18"/>
-      <c r="P52" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q52" s="51" t="s">
-        <v>2</v>
-      </c>
-      <c r="R52" s="52" t="s">
+      <c r="P52" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q52" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="R52" s="49" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53" s="18"/>
-      <c r="B53" s="61" t="s">
+      <c r="B53" s="58" t="s">
         <v>21</v>
       </c>
-      <c r="C53" s="62">
-        <v>7</v>
-      </c>
-      <c r="D53" s="63">
-        <v>5</v>
-      </c>
-      <c r="E53" s="64">
+      <c r="C53" s="59">
+        <v>7</v>
+      </c>
+      <c r="D53" s="60">
+        <v>5</v>
+      </c>
+      <c r="E53" s="61">
         <v>3</v>
       </c>
       <c r="F53" s="38"/>
-      <c r="G53" s="62">
-        <v>0</v>
-      </c>
-      <c r="H53" s="63">
-        <v>1</v>
-      </c>
-      <c r="I53" s="64">
+      <c r="G53" s="59">
+        <v>0</v>
+      </c>
+      <c r="H53" s="60">
+        <v>1</v>
+      </c>
+      <c r="I53" s="61">
         <v>0</v>
       </c>
       <c r="J53" s="36"/>
-      <c r="K53" s="62">
-        <v>7</v>
-      </c>
-      <c r="L53" s="63">
-        <v>4</v>
-      </c>
-      <c r="M53" s="64">
+      <c r="K53" s="59">
+        <v>7</v>
+      </c>
+      <c r="L53" s="60">
+        <v>4</v>
+      </c>
+      <c r="M53" s="61">
         <v>3</v>
       </c>
       <c r="N53" s="3"/>
@@ -4215,41 +4461,41 @@
     </row>
     <row r="57" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="18"/>
-      <c r="B57" s="65" t="s">
+      <c r="B57" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="C57" s="66">
-        <v>4</v>
-      </c>
-      <c r="D57" s="67">
-        <v>3</v>
-      </c>
-      <c r="E57" s="68">
+      <c r="C57" s="63">
+        <v>4</v>
+      </c>
+      <c r="D57" s="64">
+        <v>3</v>
+      </c>
+      <c r="E57" s="65">
         <v>3</v>
       </c>
       <c r="F57" s="38"/>
-      <c r="G57" s="66">
-        <v>0</v>
-      </c>
-      <c r="H57" s="67">
-        <v>0</v>
-      </c>
-      <c r="I57" s="68">
+      <c r="G57" s="63">
+        <v>0</v>
+      </c>
+      <c r="H57" s="64">
+        <v>0</v>
+      </c>
+      <c r="I57" s="65">
         <v>2</v>
       </c>
       <c r="J57" s="36"/>
-      <c r="K57" s="66">
-        <v>4</v>
-      </c>
-      <c r="L57" s="67">
-        <v>3</v>
-      </c>
-      <c r="M57" s="68">
+      <c r="K57" s="63">
+        <v>4</v>
+      </c>
+      <c r="L57" s="64">
+        <v>3</v>
+      </c>
+      <c r="M57" s="65">
         <v>1</v>
       </c>
       <c r="N57" s="3"/>
       <c r="O57" s="18"/>
-      <c r="P57" s="57" t="s">
+      <c r="P57" s="54" t="s">
         <v>16</v>
       </c>
       <c r="Q57" s="18"/>
@@ -4301,37 +4547,37 @@
       <c r="Q59" s="18"/>
       <c r="R59" s="18"/>
     </row>
-    <row r="60" spans="1:18" s="58" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="N60" s="59"/>
+    <row r="60" spans="1:18" s="55" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="N60" s="56"/>
     </row>
     <row r="61" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="62" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="18"/>
       <c r="B62" s="18"/>
-      <c r="C62" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="D62" s="44"/>
-      <c r="E62" s="45"/>
+      <c r="C62" s="73" t="s">
+        <v>4</v>
+      </c>
+      <c r="D62" s="74"/>
+      <c r="E62" s="75"/>
       <c r="F62" s="18"/>
-      <c r="G62" s="43" t="s">
+      <c r="G62" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="H62" s="44"/>
-      <c r="I62" s="45"/>
+      <c r="H62" s="74"/>
+      <c r="I62" s="75"/>
       <c r="J62" s="16"/>
-      <c r="K62" s="43" t="s">
+      <c r="K62" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="L62" s="44"/>
-      <c r="M62" s="45"/>
+      <c r="L62" s="74"/>
+      <c r="M62" s="75"/>
       <c r="N62" s="3"/>
       <c r="O62" s="18"/>
-      <c r="P62" s="43" t="s">
+      <c r="P62" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="Q62" s="44"/>
-      <c r="R62" s="45"/>
+      <c r="Q62" s="74"/>
+      <c r="R62" s="75"/>
     </row>
     <row r="63" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="18"/>
@@ -4367,48 +4613,48 @@
       </c>
       <c r="N63" s="3"/>
       <c r="O63" s="18"/>
-      <c r="P63" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q63" s="51" t="s">
-        <v>2</v>
-      </c>
-      <c r="R63" s="52" t="s">
+      <c r="P63" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q63" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="R63" s="49" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A64" s="18"/>
-      <c r="B64" s="61" t="s">
+      <c r="B64" s="58" t="s">
         <v>21</v>
       </c>
-      <c r="C64" s="62">
-        <v>7</v>
-      </c>
-      <c r="D64" s="63">
-        <v>5</v>
-      </c>
-      <c r="E64" s="64">
+      <c r="C64" s="59">
+        <v>7</v>
+      </c>
+      <c r="D64" s="60">
+        <v>5</v>
+      </c>
+      <c r="E64" s="61">
         <v>3</v>
       </c>
       <c r="F64" s="38"/>
-      <c r="G64" s="62">
-        <v>0</v>
-      </c>
-      <c r="H64" s="63">
-        <v>1</v>
-      </c>
-      <c r="I64" s="64">
+      <c r="G64" s="59">
+        <v>0</v>
+      </c>
+      <c r="H64" s="60">
+        <v>1</v>
+      </c>
+      <c r="I64" s="61">
         <v>0</v>
       </c>
       <c r="J64" s="36"/>
-      <c r="K64" s="62">
-        <v>7</v>
-      </c>
-      <c r="L64" s="63">
-        <v>4</v>
-      </c>
-      <c r="M64" s="64">
+      <c r="K64" s="59">
+        <v>7</v>
+      </c>
+      <c r="L64" s="60">
+        <v>4</v>
+      </c>
+      <c r="M64" s="61">
         <v>3</v>
       </c>
       <c r="N64" s="3"/>
@@ -4563,41 +4809,41 @@
     </row>
     <row r="68" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="18"/>
-      <c r="B68" s="65" t="s">
+      <c r="B68" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="C68" s="66">
-        <v>4</v>
-      </c>
-      <c r="D68" s="67">
-        <v>3</v>
-      </c>
-      <c r="E68" s="68">
+      <c r="C68" s="63">
+        <v>4</v>
+      </c>
+      <c r="D68" s="64">
+        <v>3</v>
+      </c>
+      <c r="E68" s="65">
         <v>3</v>
       </c>
       <c r="F68" s="38"/>
-      <c r="G68" s="66">
-        <v>0</v>
-      </c>
-      <c r="H68" s="67">
-        <v>0</v>
-      </c>
-      <c r="I68" s="68">
+      <c r="G68" s="63">
+        <v>0</v>
+      </c>
+      <c r="H68" s="64">
+        <v>0</v>
+      </c>
+      <c r="I68" s="65">
         <v>2</v>
       </c>
       <c r="J68" s="36"/>
-      <c r="K68" s="66">
-        <v>4</v>
-      </c>
-      <c r="L68" s="67">
-        <v>3</v>
-      </c>
-      <c r="M68" s="68">
+      <c r="K68" s="63">
+        <v>4</v>
+      </c>
+      <c r="L68" s="64">
+        <v>3</v>
+      </c>
+      <c r="M68" s="65">
         <v>1</v>
       </c>
       <c r="N68" s="3"/>
       <c r="O68" s="18"/>
-      <c r="P68" s="57" t="s">
+      <c r="P68" s="54" t="s">
         <v>23</v>
       </c>
       <c r="Q68" s="18"/>
@@ -4651,6 +4897,19 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="P7:R7"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="K18:M18"/>
+    <mergeCell ref="P18:R18"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="K29:M29"/>
+    <mergeCell ref="P29:R29"/>
     <mergeCell ref="C62:E62"/>
     <mergeCell ref="G62:I62"/>
     <mergeCell ref="K62:M62"/>
@@ -4663,19 +4922,414 @@
     <mergeCell ref="G51:I51"/>
     <mergeCell ref="K51:M51"/>
     <mergeCell ref="P51:R51"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="P18:R18"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="K29:M29"/>
-    <mergeCell ref="P29:R29"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="P7:R7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99B9D226-7B49-4F95-9A10-33D7CABE239D}">
+  <dimension ref="A1:M21"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="77"/>
+    <col min="2" max="2" width="9.33203125" style="77" bestFit="1" customWidth="1"/>
+    <col min="3" max="9" width="8.88671875" style="77"/>
+    <col min="10" max="10" width="4" style="77" customWidth="1"/>
+    <col min="11" max="11" width="12.44140625" style="77" customWidth="1"/>
+    <col min="12" max="12" width="11.5546875" style="77" customWidth="1"/>
+    <col min="13" max="13" width="10.6640625" style="77" customWidth="1"/>
+    <col min="14" max="14" width="12.5546875" style="77" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.88671875" style="77"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="89" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="90"/>
+      <c r="C1" s="90"/>
+      <c r="D1" s="91"/>
+    </row>
+    <row r="2" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="89" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="90"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="91"/>
+    </row>
+    <row r="3" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="78"/>
+    </row>
+    <row r="4" spans="1:13" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="105" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="104">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="6" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="114" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="79" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="85" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="89" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="90"/>
+      <c r="E7" s="90"/>
+      <c r="F7" s="90"/>
+      <c r="G7" s="90"/>
+      <c r="H7" s="91"/>
+      <c r="I7" s="101" t="s">
+        <v>38</v>
+      </c>
+      <c r="J7" s="99"/>
+      <c r="K7" s="95"/>
+      <c r="L7" s="117"/>
+    </row>
+    <row r="8" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="84"/>
+      <c r="B8" s="86"/>
+      <c r="C8" s="92">
+        <v>30</v>
+      </c>
+      <c r="D8" s="93">
+        <v>35</v>
+      </c>
+      <c r="E8" s="93">
+        <v>15</v>
+      </c>
+      <c r="F8" s="93">
+        <v>25</v>
+      </c>
+      <c r="G8" s="93">
+        <v>75</v>
+      </c>
+      <c r="H8" s="94">
+        <v>45</v>
+      </c>
+      <c r="I8" s="101">
+        <f>SUM(C8:H8)</f>
+        <v>225</v>
+      </c>
+      <c r="K8" s="101" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" s="81">
+        <v>39</v>
+      </c>
+      <c r="B9" s="87">
+        <v>40</v>
+      </c>
+      <c r="C9" s="96">
+        <v>30</v>
+      </c>
+      <c r="D9" s="97">
+        <v>35</v>
+      </c>
+      <c r="E9" s="97">
+        <v>15</v>
+      </c>
+      <c r="F9" s="97">
+        <v>25</v>
+      </c>
+      <c r="G9" s="106" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" s="98">
+        <v>45</v>
+      </c>
+      <c r="K9" s="102">
+        <f>B9-A9</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" s="81">
+        <v>40</v>
+      </c>
+      <c r="B10" s="87">
+        <v>40</v>
+      </c>
+      <c r="C10" s="80">
+        <v>30</v>
+      </c>
+      <c r="D10" s="99">
+        <v>35</v>
+      </c>
+      <c r="E10" s="99">
+        <v>15</v>
+      </c>
+      <c r="F10" s="99">
+        <v>25</v>
+      </c>
+      <c r="G10" s="99">
+        <v>35</v>
+      </c>
+      <c r="H10" s="107" t="s">
+        <v>32</v>
+      </c>
+      <c r="K10" s="87">
+        <f>B10-A10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11" s="110">
+        <v>33</v>
+      </c>
+      <c r="B11" s="111">
+        <v>36</v>
+      </c>
+      <c r="C11" s="112">
+        <v>30</v>
+      </c>
+      <c r="D11" s="113">
+        <v>35</v>
+      </c>
+      <c r="E11" s="113">
+        <v>15</v>
+      </c>
+      <c r="F11" s="113">
+        <v>25</v>
+      </c>
+      <c r="G11" s="113">
+        <v>35</v>
+      </c>
+      <c r="H11" s="110">
+        <v>5</v>
+      </c>
+      <c r="K11" s="111">
+        <f>B11-A11</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" s="81">
+        <v>20</v>
+      </c>
+      <c r="B12" s="87">
+        <v>20</v>
+      </c>
+      <c r="C12" s="108" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="99">
+        <v>35</v>
+      </c>
+      <c r="E12" s="99">
+        <v>15</v>
+      </c>
+      <c r="F12" s="99">
+        <v>25</v>
+      </c>
+      <c r="G12" s="99">
+        <v>35</v>
+      </c>
+      <c r="H12" s="81">
+        <v>5</v>
+      </c>
+      <c r="K12" s="87">
+        <f>B12-A12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="83">
+        <v>21</v>
+      </c>
+      <c r="B13" s="88">
+        <v>24</v>
+      </c>
+      <c r="C13" s="82">
+        <v>10</v>
+      </c>
+      <c r="D13" s="109" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" s="100">
+        <v>15</v>
+      </c>
+      <c r="F13" s="100">
+        <v>25</v>
+      </c>
+      <c r="G13" s="100">
+        <v>35</v>
+      </c>
+      <c r="H13" s="83">
+        <v>5</v>
+      </c>
+      <c r="K13" s="88">
+        <f>B13-A13</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K14" s="101">
+        <v>4</v>
+      </c>
+      <c r="L14" s="103" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="76"/>
+      <c r="B15" s="76"/>
+    </row>
+    <row r="16" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="89" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="91"/>
+      <c r="C16" s="92">
+        <v>10</v>
+      </c>
+      <c r="D16" s="93">
+        <v>11</v>
+      </c>
+      <c r="E16" s="93">
+        <v>15</v>
+      </c>
+      <c r="F16" s="93">
+        <v>25</v>
+      </c>
+      <c r="G16" s="93">
+        <v>35</v>
+      </c>
+      <c r="H16" s="94">
+        <v>5</v>
+      </c>
+      <c r="K16" s="89" t="s">
+        <v>41</v>
+      </c>
+      <c r="L16" s="91"/>
+      <c r="M16" s="103" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="89" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="91"/>
+      <c r="C17" s="101">
+        <v>1</v>
+      </c>
+      <c r="K17" s="115">
+        <f>(I20+I21+K14)/I8</f>
+        <v>0.25777777777777777</v>
+      </c>
+      <c r="L17" s="116"/>
+    </row>
+    <row r="18" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="19" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="89" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="91"/>
+      <c r="C19" s="101">
+        <f>MIN(B9:B13)</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="89" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="91"/>
+      <c r="C20" s="96">
+        <f>MOD(C16,B4)</f>
+        <v>2</v>
+      </c>
+      <c r="D20" s="97">
+        <f>MOD(D16,B4)</f>
+        <v>3</v>
+      </c>
+      <c r="E20" s="97">
+        <f>MOD(E16,B4)</f>
+        <v>3</v>
+      </c>
+      <c r="F20" s="97">
+        <f>MOD(F16,B4)</f>
+        <v>1</v>
+      </c>
+      <c r="G20" s="97">
+        <f>MOD(G16,B4)</f>
+        <v>3</v>
+      </c>
+      <c r="H20" s="98">
+        <f>MOD(H16,B4)</f>
+        <v>1</v>
+      </c>
+      <c r="I20" s="101">
+        <f>SUM(C20:H20)</f>
+        <v>13</v>
+      </c>
+      <c r="J20" s="99"/>
+    </row>
+    <row r="21" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="89" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="90"/>
+      <c r="C21" s="92">
+        <f>IF(C16&lt;$C$19,C16,0)</f>
+        <v>10</v>
+      </c>
+      <c r="D21" s="93">
+        <f t="shared" ref="D21:H21" si="0">IF(D16&lt;$C$19,D16,0)</f>
+        <v>11</v>
+      </c>
+      <c r="E21" s="93">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="F21" s="93">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G21" s="93">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H21" s="94">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="I21" s="94">
+        <f>SUM(C21:H21)</f>
+        <v>41</v>
+      </c>
+      <c r="J21" s="99"/>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="C7:H7"/>
+    <mergeCell ref="B7:B8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
